--- a/test_doc/new_org/teachers_staff.xlsx
+++ b/test_doc/new_org/teachers_staff.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Suresh Menon</t>
+          <t>Anil Kumar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>suresh.menon@example.com</t>
+          <t>anil.kumar@example.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,19 +456,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-A Mathematics x10; 6-B Mathematics x10; 7-A Mathematics x10</t>
+          <t>5 Mathematics x9; 5 Science x9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kavitha Rao</t>
+          <t>Sunita Verma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kavitha.rao@example.com</t>
+          <t>sunita.verma@example.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,19 +478,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6-A Science x10; 6-B Science x10; 7-A Science x10</t>
+          <t>6 Mathematics x9; 7 Mathematics x9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arjun Das</t>
+          <t>Rajesh Gupta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>arjun.das@example.com</t>
+          <t>rajesh.gupta@example.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,19 +500,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6-A English x10; 6-B English x10; 7-A English x10</t>
+          <t>6 Science x9; 7 Science x9; 5 IT x7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Meera Pillai</t>
+          <t>Priya Nair</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>meera.pillai@example.com</t>
+          <t>priya.nair@example.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,19 +522,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6-A Social Studies x9; 6-B Social Studies x9; 7-A Social Studies x9</t>
+          <t>5 English x8; 6 English x8; 7 English x8; 5 Hindi x7; 6 Hindi x7; 7 Hindi x7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farhan Sheikh</t>
+          <t>Mohan Reddy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>farhan.sheikh@example.com</t>
+          <t>mohan.reddy@example.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,46 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6-A Hindi x9; 6-B Hindi x9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Divya Nair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>divya.nair@example.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>9811100006</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9-C Astronomy x4; 7-A Hindi x9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ghost@example.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>9811100007</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6-A English x2</t>
+          <t>5 Social Studies x8; 6 Social Studies x8; 7 Social Studies x8; 6 IT x7; 7 IT x7</t>
         </is>
       </c>
     </row>

--- a/test_doc/new_org/teachers_staff.xlsx
+++ b/test_doc/new_org/teachers_staff.xlsx
@@ -441,110 +441,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anil Kumar</t>
+          <t>Anil Das</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>anil.kumar@example.com</t>
+          <t>anil.das@example.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9811100001</t>
+          <t>9811110000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5 Mathematics x9; 5 Science x9</t>
+          <t>5 English x12; 6 English x11; 7 English x8; 8 English x5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sunita Verma</t>
+          <t>Lakshmi Kumar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sunita.verma@example.com</t>
+          <t>lakshmi.kumar@example.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9811100002</t>
+          <t>9811110001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6 Mathematics x9; 7 Mathematics x9</t>
+          <t>5 Mathematics x15; 6 Mathematics x13; 7 Mathematics x5; 8 Mathematics x13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rajesh Gupta</t>
+          <t>Arun Banerjee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rajesh.gupta@example.com</t>
+          <t>arun.banerjee@example.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9811100003</t>
+          <t>9811110002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6 Science x9; 7 Science x9; 5 IT x7</t>
+          <t>5 Social Studies x6; 6 Social Studies x10; 7 Social Studies x9; 8 Social Studies x11; 5 Science x8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Priya Nair</t>
+          <t>Anjali Bose</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>priya.nair@example.com</t>
+          <t>anjali.bose@example.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9811100004</t>
+          <t>9811110003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5 English x8; 6 English x8; 7 English x8; 5 Hindi x7; 6 Hindi x7; 7 Hindi x7</t>
+          <t>6 Science x8; 7 Science x19; 8 Science x7; 5 IT x7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mohan Reddy</t>
+          <t>Deepa Naidu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mohan.reddy@example.com</t>
+          <t>deepa.naidu@example.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9811100005</t>
+          <t>9811110004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5 Social Studies x8; 6 Social Studies x8; 7 Social Studies x8; 6 IT x7; 7 IT x7</t>
+          <t>6 IT x6; 7 IT x7; 8 IT x12</t>
         </is>
       </c>
     </row>
